--- a/Inputs/Baseline.xlsx
+++ b/Inputs/Baseline.xlsx
@@ -392,10 +392,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N241"/>
+  <dimension ref="A1:O241"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,7 +413,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -421,7 +421,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -431,7 +431,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>1</v>
@@ -440,7 +440,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -449,8 +449,9 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A24" si="0">A3+1</f>
         <v>2</v>
@@ -459,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -468,8 +469,9 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -478,7 +480,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -490,7 +492,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -499,7 +501,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -508,10 +510,10 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -520,7 +522,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -529,10 +531,10 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="M7" s="1"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -541,7 +543,8 @@
         <v>2</v>
       </c>
       <c r="C8" s="2">
-        <v>3.3000000000000003</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -550,10 +553,11 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="M8" s="1"/>
       <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -562,7 +566,8 @@
         <v>2</v>
       </c>
       <c r="C9" s="2">
-        <v>0.44999999999999996</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -571,10 +576,11 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -583,7 +589,8 @@
         <v>2</v>
       </c>
       <c r="C10" s="2">
-        <v>0.6</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -592,10 +599,10 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="M10" s="1"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -604,7 +611,8 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -613,10 +621,10 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+      <c r="M11" s="1"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -625,7 +633,8 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -634,10 +643,10 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="M12" s="1"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -646,7 +655,8 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>0.70000000000000007</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -655,10 +665,10 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="M13" s="1"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -667,7 +677,8 @@
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>0.6</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -676,10 +687,10 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="M14" s="1"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -688,7 +699,8 @@
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>0.5</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -697,10 +709,10 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" s="1"/>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -709,7 +721,8 @@
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>0.35000000000000003</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -718,7 +731,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="M16" s="1"/>
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -730,7 +743,8 @@
         <v>2</v>
       </c>
       <c r="C17" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -739,7 +753,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="M17" s="1"/>
       <c r="N17" s="2"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -751,7 +765,8 @@
         <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -760,7 +775,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="M18" s="1"/>
       <c r="N18" s="2"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -772,7 +787,8 @@
         <v>2</v>
       </c>
       <c r="C19" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -781,7 +797,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+      <c r="M19" s="1"/>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -793,7 +809,8 @@
         <v>2</v>
       </c>
       <c r="C20" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -802,7 +819,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+      <c r="M20" s="1"/>
       <c r="N20" s="2"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -814,7 +831,8 @@
         <v>2</v>
       </c>
       <c r="C21" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -823,7 +841,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="M21" s="1"/>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -835,7 +853,8 @@
         <v>2</v>
       </c>
       <c r="C22" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -844,7 +863,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
+      <c r="M22" s="1"/>
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -856,7 +875,8 @@
         <v>2</v>
       </c>
       <c r="C23" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -865,7 +885,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
+      <c r="M23" s="1"/>
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -877,7 +897,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -886,7 +906,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
+      <c r="M24" s="1"/>
       <c r="N24" s="2"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -898,7 +918,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="2">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -907,7 +927,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
+      <c r="M25" s="1"/>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -918,14 +938,15 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
+      <c r="M26" s="1"/>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -937,7 +958,8 @@
         <v>3</v>
       </c>
       <c r="C27" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -956,7 +978,8 @@
         <v>3</v>
       </c>
       <c r="C28" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -975,7 +998,8 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -994,7 +1018,8 @@
         <v>3</v>
       </c>
       <c r="C30" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -1006,7 +1031,8 @@
         <v>3</v>
       </c>
       <c r="C31" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1018,7 +1044,8 @@
         <v>3</v>
       </c>
       <c r="C32" s="2">
-        <v>0.3</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1030,7 +1057,8 @@
         <v>3</v>
       </c>
       <c r="C33" s="2">
-        <v>0.44999999999999996</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1042,7 +1070,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="2">
-        <v>0.6</v>
+        <v>0.27649999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -1054,7 +1082,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="2">
-        <v>0.75</v>
+        <v>0.27649999999999997</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -1066,7 +1094,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="2">
-        <v>0.75</v>
+        <v>0.27649999999999997</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1078,7 +1106,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="2">
-        <v>0.70000000000000007</v>
+        <v>0.27649999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1090,7 +1118,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="2">
-        <v>0.6</v>
+        <v>0.27649999999999997</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1102,7 +1130,8 @@
         <v>3</v>
       </c>
       <c r="C39" s="2">
-        <v>0.5</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1114,7 +1143,8 @@
         <v>3</v>
       </c>
       <c r="C40" s="2">
-        <v>0.35000000000000003</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1126,7 +1156,8 @@
         <v>3</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1138,7 +1169,8 @@
         <v>3</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1150,7 +1182,8 @@
         <v>3</v>
       </c>
       <c r="C43" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -1162,7 +1195,8 @@
         <v>3</v>
       </c>
       <c r="C44" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -1174,7 +1208,8 @@
         <v>3</v>
       </c>
       <c r="C45" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -1186,7 +1221,8 @@
         <v>3</v>
       </c>
       <c r="C46" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1198,7 +1234,8 @@
         <v>3</v>
       </c>
       <c r="C47" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -1210,7 +1247,8 @@
         <v>3</v>
       </c>
       <c r="C48" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -1222,7 +1260,8 @@
         <v>3</v>
       </c>
       <c r="C49" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1233,7 +1272,8 @@
         <v>4</v>
       </c>
       <c r="C50" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -1245,7 +1285,8 @@
         <v>4</v>
       </c>
       <c r="C51" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -1257,7 +1298,8 @@
         <v>4</v>
       </c>
       <c r="C52" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -1269,7 +1311,8 @@
         <v>4</v>
       </c>
       <c r="C53" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -1281,7 +1324,8 @@
         <v>4</v>
       </c>
       <c r="C54" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -1293,7 +1337,8 @@
         <v>4</v>
       </c>
       <c r="C55" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -1305,7 +1350,8 @@
         <v>4</v>
       </c>
       <c r="C56" s="2">
-        <v>0.3</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -1317,7 +1363,8 @@
         <v>4</v>
       </c>
       <c r="C57" s="2">
-        <v>0.44999999999999996</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1329,7 +1376,8 @@
         <v>4</v>
       </c>
       <c r="C58" s="2">
-        <v>0.6</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1341,7 +1389,8 @@
         <v>4</v>
       </c>
       <c r="C59" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1353,7 +1402,8 @@
         <v>4</v>
       </c>
       <c r="C60" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1365,7 +1415,8 @@
         <v>4</v>
       </c>
       <c r="C61" s="2">
-        <v>0.70000000000000007</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1377,7 +1428,8 @@
         <v>4</v>
       </c>
       <c r="C62" s="2">
-        <v>0.6</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1389,7 +1441,8 @@
         <v>4</v>
       </c>
       <c r="C63" s="2">
-        <v>0.5</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1401,7 +1454,8 @@
         <v>4</v>
       </c>
       <c r="C64" s="2">
-        <v>0.35000000000000003</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -1413,7 +1467,8 @@
         <v>4</v>
       </c>
       <c r="C65" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1425,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="C66" s="2">
-        <v>0</v>
+        <v>0.19879999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1437,7 +1492,7 @@
         <v>4</v>
       </c>
       <c r="C67" s="2">
-        <v>0</v>
+        <v>0.19879999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1449,7 +1504,7 @@
         <v>4</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>0.19879999999999998</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -1461,7 +1516,7 @@
         <v>4</v>
       </c>
       <c r="C69" s="2">
-        <v>0</v>
+        <v>0.19879999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1473,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="2">
-        <v>0</v>
+        <v>0.19879999999999998</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1485,7 +1540,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="2">
-        <v>0</v>
+        <v>0.19879999999999998</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1497,7 +1552,8 @@
         <v>4</v>
       </c>
       <c r="C72" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1509,7 +1565,8 @@
         <v>4</v>
       </c>
       <c r="C73" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -1520,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="C74" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -1532,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -1544,7 +1601,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1556,7 +1613,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1568,7 +1625,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1580,7 +1637,7 @@
         <v>5</v>
       </c>
       <c r="C79" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -1592,7 +1649,7 @@
         <v>5</v>
       </c>
       <c r="C80" s="2">
-        <v>0.3</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -1604,7 +1661,8 @@
         <v>5</v>
       </c>
       <c r="C81" s="2">
-        <v>0.44999999999999996</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -1616,7 +1674,8 @@
         <v>5</v>
       </c>
       <c r="C82" s="2">
-        <v>0.6</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -1628,7 +1687,8 @@
         <v>5</v>
       </c>
       <c r="C83" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -1640,7 +1700,8 @@
         <v>5</v>
       </c>
       <c r="C84" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -1652,7 +1713,8 @@
         <v>5</v>
       </c>
       <c r="C85" s="2">
-        <v>0.70000000000000007</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -1664,7 +1726,8 @@
         <v>5</v>
       </c>
       <c r="C86" s="2">
-        <v>0.6</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -1676,7 +1739,8 @@
         <v>5</v>
       </c>
       <c r="C87" s="2">
-        <v>0.5</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -1688,7 +1752,8 @@
         <v>5</v>
       </c>
       <c r="C88" s="2">
-        <v>0.35000000000000003</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -1700,7 +1765,8 @@
         <v>5</v>
       </c>
       <c r="C89" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -1712,7 +1778,8 @@
         <v>5</v>
       </c>
       <c r="C90" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -1724,7 +1791,8 @@
         <v>5</v>
       </c>
       <c r="C91" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -1736,7 +1804,8 @@
         <v>5</v>
       </c>
       <c r="C92" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -1748,7 +1817,8 @@
         <v>5</v>
       </c>
       <c r="C93" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -1760,7 +1830,8 @@
         <v>5</v>
       </c>
       <c r="C94" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -1772,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="C95" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -1784,7 +1855,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -1796,7 +1867,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="2">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -1807,7 +1878,8 @@
         <v>6</v>
       </c>
       <c r="C98" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -1819,7 +1891,8 @@
         <v>6</v>
       </c>
       <c r="C99" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -1831,7 +1904,8 @@
         <v>6</v>
       </c>
       <c r="C100" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -1843,7 +1917,8 @@
         <v>6</v>
       </c>
       <c r="C101" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -1855,7 +1930,8 @@
         <v>6</v>
       </c>
       <c r="C102" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -1867,7 +1943,8 @@
         <v>6</v>
       </c>
       <c r="C103" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -1879,7 +1956,8 @@
         <v>6</v>
       </c>
       <c r="C104" s="2">
-        <v>0.3</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -1891,7 +1969,8 @@
         <v>6</v>
       </c>
       <c r="C105" s="2">
-        <v>0.44999999999999996</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -1903,7 +1982,8 @@
         <v>6</v>
       </c>
       <c r="C106" s="2">
-        <v>0.6</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -1915,7 +1995,8 @@
         <v>6</v>
       </c>
       <c r="C107" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -1927,7 +2008,8 @@
         <v>6</v>
       </c>
       <c r="C108" s="2">
-        <v>0.75</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -1939,7 +2021,8 @@
         <v>6</v>
       </c>
       <c r="C109" s="2">
-        <v>0.70000000000000007</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -1951,7 +2034,7 @@
         <v>6</v>
       </c>
       <c r="C110" s="2">
-        <v>0.6</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -1963,7 +2046,7 @@
         <v>6</v>
       </c>
       <c r="C111" s="2">
-        <v>0.5</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -1975,7 +2058,7 @@
         <v>6</v>
       </c>
       <c r="C112" s="2">
-        <v>0.35000000000000003</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -1987,7 +2070,7 @@
         <v>6</v>
       </c>
       <c r="C113" s="2">
-        <v>0</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -1999,7 +2082,7 @@
         <v>6</v>
       </c>
       <c r="C114" s="2">
-        <v>0</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -2011,7 +2094,7 @@
         <v>6</v>
       </c>
       <c r="C115" s="2">
-        <v>0</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -2023,7 +2106,7 @@
         <v>6</v>
       </c>
       <c r="C116" s="2">
-        <v>0</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -2035,7 +2118,7 @@
         <v>6</v>
       </c>
       <c r="C117" s="2">
-        <v>0</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -2047,7 +2130,7 @@
         <v>6</v>
       </c>
       <c r="C118" s="2">
-        <v>0</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -2059,7 +2142,7 @@
         <v>6</v>
       </c>
       <c r="C119" s="2">
-        <v>0</v>
+        <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -2071,7 +2154,8 @@
         <v>6</v>
       </c>
       <c r="C120" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -2083,7 +2167,8 @@
         <v>6</v>
       </c>
       <c r="C121" s="2">
-        <v>0</v>
+        <f>(0.584/5)*0.7</f>
+        <v>8.1759999999999985E-2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -2568,6 +2653,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Inputs/Baseline.xlsx
+++ b/Inputs/Baseline.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="6">
   <si>
     <t>t</t>
   </si>
@@ -31,12 +31,6 @@
   </si>
   <si>
     <t>TR03</t>
-  </si>
-  <si>
-    <t>TR04</t>
-  </si>
-  <si>
-    <t>TR05</t>
   </si>
   <si>
     <t>p_base</t>
@@ -403,7 +397,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -421,7 +415,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -440,7 +434,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -460,7 +454,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -480,7 +474,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -501,7 +495,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -522,7 +516,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -543,8 +537,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -566,8 +559,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -589,8 +581,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -611,8 +602,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -633,8 +623,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -655,8 +644,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -677,8 +665,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -699,8 +686,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -721,8 +707,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -743,8 +728,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -765,8 +749,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -787,8 +770,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -809,8 +791,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -831,8 +812,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -853,8 +833,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -875,8 +854,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -897,7 +875,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -918,7 +896,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="2">
-        <v>0.161</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -938,8 +916,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -958,8 +935,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -978,8 +954,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -998,8 +973,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -1018,8 +992,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -1031,8 +1004,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1044,8 +1016,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1057,8 +1028,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1070,7 +1040,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="2">
-        <v>0.27649999999999997</v>
+        <v>0.13420000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -1082,7 +1052,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="2">
-        <v>0.27649999999999997</v>
+        <v>0.13420000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -1094,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="2">
-        <v>0.27649999999999997</v>
+        <v>0.13420000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1106,7 +1076,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="2">
-        <v>0.27649999999999997</v>
+        <v>0.13420000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1118,7 +1088,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="2">
-        <v>0.27649999999999997</v>
+        <v>0.13420000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1130,8 +1100,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1143,8 +1112,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1156,8 +1124,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1169,8 +1136,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1182,8 +1148,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -1195,8 +1160,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -1208,8 +1172,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -1221,8 +1184,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1234,8 +1196,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -1247,8 +1208,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -1260,8 +1220,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1272,8 +1231,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -1285,8 +1243,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -1298,8 +1255,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -1311,8 +1267,7 @@
         <v>4</v>
       </c>
       <c r="C53" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -1324,8 +1279,7 @@
         <v>4</v>
       </c>
       <c r="C54" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -1337,8 +1291,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -1350,8 +1303,7 @@
         <v>4</v>
       </c>
       <c r="C56" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -1363,8 +1315,7 @@
         <v>4</v>
       </c>
       <c r="C57" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1376,8 +1327,7 @@
         <v>4</v>
       </c>
       <c r="C58" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1389,8 +1339,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1402,8 +1351,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1415,8 +1363,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1428,8 +1375,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1441,8 +1387,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1454,8 +1399,7 @@
         <v>4</v>
       </c>
       <c r="C64" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -1467,8 +1411,7 @@
         <v>4</v>
       </c>
       <c r="C65" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1480,7 +1423,7 @@
         <v>4</v>
       </c>
       <c r="C66" s="2">
-        <v>0.19879999999999998</v>
+        <v>9.69E-2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1492,7 +1435,7 @@
         <v>4</v>
       </c>
       <c r="C67" s="2">
-        <v>0.19879999999999998</v>
+        <v>9.69E-2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1504,7 +1447,7 @@
         <v>4</v>
       </c>
       <c r="C68" s="2">
-        <v>0.19879999999999998</v>
+        <v>9.69E-2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -1516,7 +1459,7 @@
         <v>4</v>
       </c>
       <c r="C69" s="2">
-        <v>0.19879999999999998</v>
+        <v>9.69E-2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1528,7 +1471,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="2">
-        <v>0.19879999999999998</v>
+        <v>9.69E-2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1540,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="2">
-        <v>0.19879999999999998</v>
+        <v>9.69E-2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1552,8 +1495,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1565,611 +1507,248 @@
         <v>4</v>
       </c>
       <c r="C73" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
-        <v>0</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
-        <f>A74+1</f>
-        <v>1</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
-        <f t="shared" ref="A76:A96" si="3">A75+1</f>
-        <v>2</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C82" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C95" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C96" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
-        <f>A96+1</f>
-        <v>23</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C97" s="2">
-        <v>0.1477</v>
-      </c>
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>0</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <f>A98+1</f>
-        <v>1</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
-        <f t="shared" ref="A100:A120" si="4">A99+1</f>
-        <v>2</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="2">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="2">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C110" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="2">
-        <f t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C111" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="2">
-        <f t="shared" si="4"/>
-        <v>14</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C112" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="2">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C113" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="2">
-        <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C114" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="2">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="2">
-        <f t="shared" si="4"/>
-        <v>18</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C116" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="2">
-        <f t="shared" si="4"/>
-        <v>19</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C117" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="2">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="2">
-        <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C119" s="2">
-        <v>0.13299999999999998</v>
-      </c>
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="2">
-        <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C120" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="2">
-        <f>A120+1</f>
-        <v>23</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C121" s="2">
-        <f>(0.584/5)*0.7</f>
-        <v>8.1759999999999985E-2</v>
-      </c>
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="2"/>
